--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2019_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:01</t>
+    <t xml:space="preserve">2026-09-24 00:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -919,19 +919,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="20">
@@ -942,19 +942,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21">
@@ -968,13 +968,13 @@
         <v>0.36</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.46</v>
